--- a/artfynd/A 31510-2026 artfynd.xlsx
+++ b/artfynd/A 31510-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134351305</v>
       </c>
       <c r="B2" t="n">
-        <v>42875</v>
+        <v>42903</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>

--- a/artfynd/A 31510-2026 artfynd.xlsx
+++ b/artfynd/A 31510-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134351305</v>
       </c>
       <c r="B2" t="n">
-        <v>42903</v>
+        <v>42916</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31510-2026 artfynd.xlsx
+++ b/artfynd/A 31510-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134351305</v>
       </c>
       <c r="B2" t="n">
-        <v>42916</v>
+        <v>42918</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31510-2026 artfynd.xlsx
+++ b/artfynd/A 31510-2026 artfynd.xlsx
@@ -714,16 +714,8 @@
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>

--- a/artfynd/A 31510-2026 artfynd.xlsx
+++ b/artfynd/A 31510-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134351305</v>
       </c>
       <c r="B2" t="n">
-        <v>42918</v>
+        <v>42928</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31510-2026 artfynd.xlsx
+++ b/artfynd/A 31510-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134351305</v>
       </c>
       <c r="B2" t="n">
-        <v>42928</v>
+        <v>42929</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
